--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C5F8A4-9F77-46B1-AAA8-EC4A0E6B1948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0E449C-734C-498A-93D5-F1393C655AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Div</t>
   </si>
@@ -44,6 +44,15 @@
   </si>
   <si>
     <t>Marseille</t>
+  </si>
+  <si>
+    <t>SP1</t>
+  </si>
+  <si>
+    <t>Ath Madrid</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
   </si>
 </sst>
 </file>
@@ -447,7 +456,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="C2" s="3">
         <v>0.97916666666666663</v>
@@ -460,7 +469,21 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="2"/>
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46030</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0E449C-734C-498A-93D5-F1393C655AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60EADD5-2A48-4AA5-90FA-8EB05B7E7186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12504" yWindow="1116" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="956">
   <si>
     <t>Div</t>
   </si>
@@ -37,22 +38,2857 @@
     <t>Visitante</t>
   </si>
   <si>
-    <t>E0</t>
-  </si>
-  <si>
     <t>Paris SG</t>
   </si>
   <si>
     <t>Marseille</t>
   </si>
   <si>
-    <t>SP1</t>
-  </si>
-  <si>
     <t>Ath Madrid</t>
   </si>
   <si>
     <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
+    <t>Brighton</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Sheffield United</t>
+  </si>
+  <si>
+    <t>Newcastle</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Man United</t>
+  </si>
+  <si>
+    <t>Nott'm Forest</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Wolves</t>
+  </si>
+  <si>
+    <t>Tottenham</t>
+  </si>
+  <si>
+    <t>Man City</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>West Ham</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Luton</t>
+  </si>
+  <si>
+    <t>Sheffield Weds</t>
+  </si>
+  <si>
+    <t>Blackburn</t>
+  </si>
+  <si>
+    <t>Bristol City</t>
+  </si>
+  <si>
+    <t>Middlesbrough</t>
+  </si>
+  <si>
+    <t>Norwich</t>
+  </si>
+  <si>
+    <t>Plymouth</t>
+  </si>
+  <si>
+    <t>Stoke</t>
+  </si>
+  <si>
+    <t>Swansea</t>
+  </si>
+  <si>
+    <t>Watford</t>
+  </si>
+  <si>
+    <t>Leicester</t>
+  </si>
+  <si>
+    <t>Leeds</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Coventry</t>
+  </si>
+  <si>
+    <t>Birmingham</t>
+  </si>
+  <si>
+    <t>Cardiff</t>
+  </si>
+  <si>
+    <t>Huddersfield</t>
+  </si>
+  <si>
+    <t>Hull</t>
+  </si>
+  <si>
+    <t>Ipswich</t>
+  </si>
+  <si>
+    <t>Millwall</t>
+  </si>
+  <si>
+    <t>Preston</t>
+  </si>
+  <si>
+    <t>Rotherham</t>
+  </si>
+  <si>
+    <t>Southampton</t>
+  </si>
+  <si>
+    <t>West Brom</t>
+  </si>
+  <si>
+    <t>QPR</t>
+  </si>
+  <si>
+    <t>Barnsley</t>
+  </si>
+  <si>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>Bolton</t>
+  </si>
+  <si>
+    <t>Cambridge</t>
+  </si>
+  <si>
+    <t>Carlisle</t>
+  </si>
+  <si>
+    <t>Charlton</t>
+  </si>
+  <si>
+    <t>Derby</t>
+  </si>
+  <si>
+    <t>Northampton</t>
+  </si>
+  <si>
+    <t>Portsmouth</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Shrewsbury</t>
+  </si>
+  <si>
+    <t>Wycombe</t>
+  </si>
+  <si>
+    <t>Bristol Rvs</t>
+  </si>
+  <si>
+    <t>Burton</t>
+  </si>
+  <si>
+    <t>Cheltenham</t>
+  </si>
+  <si>
+    <t>Exeter</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Leyton Orient</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
+  </si>
+  <si>
+    <t>Oxford</t>
+  </si>
+  <si>
+    <t>Peterboro</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Wigan</t>
+  </si>
+  <si>
+    <t>Accrington</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Crewe</t>
+  </si>
+  <si>
+    <t>Doncaster</t>
+  </si>
+  <si>
+    <t>Forest Green</t>
+  </si>
+  <si>
+    <t>Grimsby</t>
+  </si>
+  <si>
+    <t>Morecambe</t>
+  </si>
+  <si>
+    <t>Stockport</t>
+  </si>
+  <si>
+    <t>Sutton</t>
+  </si>
+  <si>
+    <t>Tranmere</t>
+  </si>
+  <si>
+    <t>Wrexham</t>
+  </si>
+  <si>
+    <t>AFC Wimbledon</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Bradford</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Harrogate</t>
+  </si>
+  <si>
+    <t>Mansfield</t>
+  </si>
+  <si>
+    <t>Milton Keynes Dons</t>
+  </si>
+  <si>
+    <t>Newport County</t>
+  </si>
+  <si>
+    <t>Notts County</t>
+  </si>
+  <si>
+    <t>Salford</t>
+  </si>
+  <si>
+    <t>Swindon</t>
+  </si>
+  <si>
+    <t>Walsall</t>
+  </si>
+  <si>
+    <t>Colchester</t>
+  </si>
+  <si>
+    <t>Aldershot</t>
+  </si>
+  <si>
+    <t>Altrincham</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>Gateshead</t>
+  </si>
+  <si>
+    <t>Halifax</t>
+  </si>
+  <si>
+    <t>Kidderminster</t>
+  </si>
+  <si>
+    <t>Maidenhead</t>
+  </si>
+  <si>
+    <t>Solihull</t>
+  </si>
+  <si>
+    <t>Southend</t>
+  </si>
+  <si>
+    <t>Wealdstone</t>
+  </si>
+  <si>
+    <t>Rochdale</t>
+  </si>
+  <si>
+    <t>Boreham Wood</t>
+  </si>
+  <si>
+    <t>Dag and Red</t>
+  </si>
+  <si>
+    <t>Dorking</t>
+  </si>
+  <si>
+    <t>Eastleigh</t>
+  </si>
+  <si>
+    <t>Ebbsfleet</t>
+  </si>
+  <si>
+    <t>Fylde</t>
+  </si>
+  <si>
+    <t>Hartlepool</t>
+  </si>
+  <si>
+    <t>Oldham</t>
+  </si>
+  <si>
+    <t>Oxford City</t>
+  </si>
+  <si>
+    <t>Woking</t>
+  </si>
+  <si>
+    <t>York</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>St Johnstone</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Ross County</t>
+  </si>
+  <si>
+    <t>St Mirren</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Arbroath</t>
+  </si>
+  <si>
+    <t>Dunfermline</t>
+  </si>
+  <si>
+    <t>Inverness C</t>
+  </si>
+  <si>
+    <t>Morton</t>
+  </si>
+  <si>
+    <t>Partick</t>
+  </si>
+  <si>
+    <t>Airdrie Utd</t>
+  </si>
+  <si>
+    <t>Ayr</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Queens Park</t>
+  </si>
+  <si>
+    <t>Raith Rvs</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t>Montrose</t>
+  </si>
+  <si>
+    <t>Queen of Sth</t>
+  </si>
+  <si>
+    <t>Stirling</t>
+  </si>
+  <si>
+    <t>Alloa</t>
+  </si>
+  <si>
+    <t>Annan Athletic</t>
+  </si>
+  <si>
+    <t>Cove Rangers</t>
+  </si>
+  <si>
+    <t>Edinburgh City</t>
+  </si>
+  <si>
+    <t>Kelty Hearts</t>
+  </si>
+  <si>
+    <t>Bonnyrigg Rose</t>
+  </si>
+  <si>
+    <t>East Fife</t>
+  </si>
+  <si>
+    <t>Elgin</t>
+  </si>
+  <si>
+    <t>Spartans</t>
+  </si>
+  <si>
+    <t>Stenhousemuir</t>
+  </si>
+  <si>
+    <t>Clyde</t>
+  </si>
+  <si>
+    <t>Dumbarton</t>
+  </si>
+  <si>
+    <t>Forfar</t>
+  </si>
+  <si>
+    <t>Peterhead</t>
+  </si>
+  <si>
+    <t>Stranraer</t>
+  </si>
+  <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
+    <t>Leverkusen</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
+    <t>Dortmund</t>
+  </si>
+  <si>
+    <t>Union Berlin</t>
+  </si>
+  <si>
+    <t>Ein Frankfurt</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Darmstadt</t>
+  </si>
+  <si>
+    <t>FC Koln</t>
+  </si>
+  <si>
+    <t>Freiburg</t>
+  </si>
+  <si>
+    <t>Heidenheim</t>
+  </si>
+  <si>
+    <t>M'gladbach</t>
+  </si>
+  <si>
+    <t>Mainz</t>
+  </si>
+  <si>
+    <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>Hannover</t>
+  </si>
+  <si>
+    <t>Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Osnabruck</t>
+  </si>
+  <si>
+    <t>Wehen</t>
+  </si>
+  <si>
+    <t>Fortuna Dusseldorf</t>
+  </si>
+  <si>
+    <t>Braunschweig</t>
+  </si>
+  <si>
+    <t>Greuther Furth</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Hertha</t>
+  </si>
+  <si>
+    <t>Paderborn</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>St Pauli</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Karlsruhe</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Nurnberg</t>
+  </si>
+  <si>
+    <t>Almeria</t>
+  </si>
+  <si>
+    <t>Sevilla</t>
+  </si>
+  <si>
+    <t>Sociedad</t>
+  </si>
+  <si>
+    <t>Las Palmas</t>
+  </si>
+  <si>
+    <t>Ath Bilbao</t>
+  </si>
+  <si>
+    <t>Celta</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Getafe</t>
+  </si>
+  <si>
+    <t>Cadiz</t>
+  </si>
+  <si>
+    <t>Mallorca</t>
+  </si>
+  <si>
+    <t>Valencia</t>
+  </si>
+  <si>
+    <t>Osasuna</t>
+  </si>
+  <si>
+    <t>Girona</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Betis</t>
+  </si>
+  <si>
+    <t>Alaves</t>
+  </si>
+  <si>
+    <t>Granada</t>
+  </si>
+  <si>
+    <t>Vallecano</t>
+  </si>
+  <si>
+    <t>Amorebieta</t>
+  </si>
+  <si>
+    <t>Valladolid</t>
+  </si>
+  <si>
+    <t>Santander</t>
+  </si>
+  <si>
+    <t>Zaragoza</t>
+  </si>
+  <si>
+    <t>Elche</t>
+  </si>
+  <si>
+    <t>Burgos</t>
+  </si>
+  <si>
+    <t>Albacete</t>
+  </si>
+  <si>
+    <t>Cartagena</t>
+  </si>
+  <si>
+    <t>Leganes</t>
+  </si>
+  <si>
+    <t>Mirandes</t>
+  </si>
+  <si>
+    <t>Tenerife</t>
+  </si>
+  <si>
+    <t>Andorra</t>
+  </si>
+  <si>
+    <t>Eibar</t>
+  </si>
+  <si>
+    <t>Espanol</t>
+  </si>
+  <si>
+    <t>Levante</t>
+  </si>
+  <si>
+    <t>Alcorcon</t>
+  </si>
+  <si>
+    <t>Oviedo</t>
+  </si>
+  <si>
+    <t>Sp Gijon</t>
+  </si>
+  <si>
+    <t>Villarreal B</t>
+  </si>
+  <si>
+    <t>Huesca</t>
+  </si>
+  <si>
+    <t>Ferrol</t>
+  </si>
+  <si>
+    <t>Eldense</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Inter</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Lecce</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Bologna</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Verona</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Juventus</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Napoli</t>
+  </si>
+  <si>
+    <t>Salernitana</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Atalanta</t>
+  </si>
+  <si>
+    <t>Bari</t>
+  </si>
+  <si>
+    <t>Cosenza</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Ternana</t>
+  </si>
+  <si>
+    <t>Sudtirol</t>
+  </si>
+  <si>
+    <t>Cittadella</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Como</t>
+  </si>
+  <si>
+    <t>FeralpiSalo</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Ascoli</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Brescia</t>
+  </si>
+  <si>
+    <t>Lecco</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>Brest</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
+    <t>Metz</t>
+  </si>
+  <si>
+    <t>Lyon</t>
+  </si>
+  <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Le Havre</t>
+  </si>
+  <si>
+    <t>Lorient</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>St Etienne</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>Amiens</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Paris FC</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Pau FC</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Angers</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Grenoble</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Bordeaux</t>
+  </si>
+  <si>
+    <t>St. Gilloise</t>
+  </si>
+  <si>
+    <t>Eupen</t>
+  </si>
+  <si>
+    <t>Charleroi</t>
+  </si>
+  <si>
+    <t>RWD Molenbeek</t>
+  </si>
+  <si>
+    <t>Antwerp</t>
+  </si>
+  <si>
+    <t>Gent</t>
+  </si>
+  <si>
+    <t>Club Brugge</t>
+  </si>
+  <si>
+    <t>St Truiden</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Genk</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Oud-Heverlee Leuven</t>
+  </si>
+  <si>
+    <t>Anderlecht</t>
+  </si>
+  <si>
+    <t>Mechelen</t>
+  </si>
+  <si>
+    <t>Westerlo</t>
+  </si>
+  <si>
+    <t>Kortrijk</t>
+  </si>
+  <si>
+    <t>Volendam</t>
+  </si>
+  <si>
+    <t>PSV Eindhoven</t>
+  </si>
+  <si>
+    <t>Heerenveen</t>
+  </si>
+  <si>
+    <t>Ajax</t>
+  </si>
+  <si>
+    <t>Zwolle</t>
+  </si>
+  <si>
+    <t>Nijmegen</t>
+  </si>
+  <si>
+    <t>AZ Alkmaar</t>
+  </si>
+  <si>
+    <t>Feyenoord</t>
+  </si>
+  <si>
+    <t>Almere City</t>
+  </si>
+  <si>
+    <t>Heracles</t>
+  </si>
+  <si>
+    <t>Excelsior</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>For Sittard</t>
+  </si>
+  <si>
+    <t>Go Ahead Eagles</t>
+  </si>
+  <si>
+    <t>Utrecht</t>
+  </si>
+  <si>
+    <t>Sparta Rotterdam</t>
+  </si>
+  <si>
+    <t>Twente</t>
+  </si>
+  <si>
+    <t>Waalwijk</t>
+  </si>
+  <si>
+    <t>Sp Braga</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Sp Lisbon</t>
+  </si>
+  <si>
+    <t>Rio Ave</t>
+  </si>
+  <si>
+    <t>Estrela</t>
+  </si>
+  <si>
+    <t>Arouca</t>
+  </si>
+  <si>
+    <t>Moreirense</t>
+  </si>
+  <si>
+    <t>Boavista</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Guimaraes</t>
+  </si>
+  <si>
+    <t>Chaves</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Estoril</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Vizela</t>
+  </si>
+  <si>
+    <t>Famalicao</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Kasimpasa</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Pendikspor</t>
+  </si>
+  <si>
+    <t>Sivasspor</t>
+  </si>
+  <si>
+    <t>Ad. Demirspor</t>
+  </si>
+  <si>
+    <t>Fenerbahce</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Karagumruk</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Istanbulspor</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Hatayspor</t>
+  </si>
+  <si>
+    <t>Buyuksehyr</t>
+  </si>
+  <si>
+    <t>Besiktas</t>
+  </si>
+  <si>
+    <t>Gaziantep</t>
+  </si>
+  <si>
+    <t>Ankaragucu</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Volos NFC</t>
+  </si>
+  <si>
+    <t>Giannina</t>
+  </si>
+  <si>
+    <t>OFI Crete</t>
+  </si>
+  <si>
+    <t>PAOK</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Panetolikos</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>AEK</t>
+  </si>
+  <si>
+    <t>Lamia</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
+    <t>Boston Utd</t>
+  </si>
+  <si>
+    <t>Tamworth</t>
+  </si>
+  <si>
+    <t>Yeovil</t>
+  </si>
+  <si>
+    <t>Braintree Town</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Regensburg</t>
+  </si>
+  <si>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>La Coruna</t>
+  </si>
+  <si>
+    <t>Malaga</t>
+  </si>
+  <si>
+    <t>Castellon</t>
+  </si>
+  <si>
+    <t>Cordoba</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Martigues</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Beerschot VA</t>
+  </si>
+  <si>
+    <t>Dender</t>
+  </si>
+  <si>
+    <t>Groningen</t>
+  </si>
+  <si>
+    <t>Willem II</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Nacional</t>
+  </si>
+  <si>
+    <t>Bodrumspor</t>
+  </si>
+  <si>
+    <t>Goztep</t>
+  </si>
+  <si>
+    <t>Eyupspor</t>
+  </si>
+  <si>
+    <t>Levadeiakos</t>
+  </si>
+  <si>
+    <t>Athens Kallithea</t>
+  </si>
+  <si>
+    <t>Brackley Town</t>
+  </si>
+  <si>
+    <t>Scunthorpe</t>
+  </si>
+  <si>
+    <t>Truro</t>
+  </si>
+  <si>
+    <t>East Kilbride</t>
+  </si>
+  <si>
+    <t>Bielefeld</t>
+  </si>
+  <si>
+    <t>Dresden</t>
+  </si>
+  <si>
+    <t>Sociedad B</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Cultural Leonesa</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Padova</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Waregem</t>
+  </si>
+  <si>
+    <t>RAAL La Louviere</t>
+  </si>
+  <si>
+    <t>Telstar</t>
+  </si>
+  <si>
+    <t>Tondela</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Genclerbirligi</t>
+  </si>
+  <si>
+    <t>Larisa</t>
+  </si>
+  <si>
+    <t>Arsenal Sarandi</t>
+  </si>
+  <si>
+    <t>Velez Sarsfield</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Colon Santa FE</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Newells Old Boys</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>San Martin S.J.</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>Estudiantes L.P.</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Argentinos Jrs</t>
+  </si>
+  <si>
+    <t>Union de Santa Fe</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Atl. Rafaela</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Gimnasia L.P.</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Olimpo Bahia Blanca</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Crucero del Norte</t>
+  </si>
+  <si>
+    <t>Sarmiento Junin</t>
+  </si>
+  <si>
+    <t>Huracan</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Atl. Tucuman</t>
+  </si>
+  <si>
+    <t>Talleres Cordoba</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>San Martin T.</t>
+  </si>
+  <si>
+    <t>Central Cordoba</t>
+  </si>
+  <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Colon Santa Fe</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Ind. Rivadavia</t>
+  </si>
+  <si>
+    <t>Dep. Riestra</t>
+  </si>
+  <si>
+    <t>Sturm Graz</t>
+  </si>
+  <si>
+    <t>Mattersburg</t>
+  </si>
+  <si>
+    <t>SK Rapid</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Austria Vienna</t>
+  </si>
+  <si>
+    <t>Neustadt</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Wacker Innsbruck</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Grodig</t>
+  </si>
+  <si>
+    <t>Altach</t>
+  </si>
+  <si>
+    <t>St. Polten</t>
+  </si>
+  <si>
+    <t>LASK</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>Tirol</t>
+  </si>
+  <si>
+    <t>A. Klagenfurt</t>
+  </si>
+  <si>
+    <t>A. Lustenau</t>
+  </si>
+  <si>
+    <t>BW Linz</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Botafogo RJ</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Vasco</t>
+  </si>
+  <si>
+    <t>Atletico GO</t>
+  </si>
+  <si>
+    <t>Flamengo RJ</t>
+  </si>
+  <si>
+    <t>Portuguesa</t>
+  </si>
+  <si>
+    <t>Nautico</t>
+  </si>
+  <si>
+    <t>Atletico-MG</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Sao Paulo</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Gremio</t>
+  </si>
+  <si>
+    <t>Vitoria</t>
+  </si>
+  <si>
+    <t>Criciuma</t>
+  </si>
+  <si>
+    <t>Athletico-PR</t>
+  </si>
+  <si>
+    <t>Goias</t>
+  </si>
+  <si>
+    <t>Chapecoense-SC</t>
+  </si>
+  <si>
+    <t>Avai</t>
+  </si>
+  <si>
+    <t>Joinville</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>America MG</t>
+  </si>
+  <si>
+    <t>Parana</t>
+  </si>
+  <si>
+    <t>Ceara</t>
+  </si>
+  <si>
+    <t>CSA</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Cuiaba</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Guangzhou Evergrande</t>
+  </si>
+  <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
+    <t>Hangzhou Greentown</t>
+  </si>
+  <si>
+    <t>Jiangsu Suning</t>
+  </si>
+  <si>
+    <t>Liaoning</t>
+  </si>
+  <si>
+    <t>Shanghai Shenxin</t>
+  </si>
+  <si>
+    <t>Tianjin Jinmen Tiger</t>
+  </si>
+  <si>
+    <t>Dalian Yifang F.C.</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Beijing Renhe</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
+    <t>Guangzhou R&amp;F</t>
+  </si>
+  <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
+    <t>Henan Songshan Longmen</t>
+  </si>
+  <si>
+    <t>Zhejiang Yiteng</t>
+  </si>
+  <si>
+    <t>Chongqing Liangjiang Athletic</t>
+  </si>
+  <si>
+    <t>Shijiazhuang</t>
+  </si>
+  <si>
+    <t>Yanbian</t>
+  </si>
+  <si>
+    <t>Hebei</t>
+  </si>
+  <si>
+    <t>Guizhou Zhicheng</t>
+  </si>
+  <si>
+    <t>Tianjin Quanjian</t>
+  </si>
+  <si>
+    <t>Wuhan FC</t>
+  </si>
+  <si>
+    <t>Shenzhen</t>
+  </si>
+  <si>
+    <t>Tianjin Tianhai</t>
+  </si>
+  <si>
+    <t>Dalian Pro</t>
+  </si>
+  <si>
+    <t>Qingdao FC</t>
+  </si>
+  <si>
+    <t>Zhejiang Greentown</t>
+  </si>
+  <si>
+    <t>Guangzhou FC</t>
+  </si>
+  <si>
+    <t>Guangzhou City</t>
+  </si>
+  <si>
+    <t>Shandong Taishan</t>
+  </si>
+  <si>
+    <t>Cangzhou</t>
+  </si>
+  <si>
+    <t>Shanghai Port</t>
+  </si>
+  <si>
+    <t>Chengdu Rongcheng</t>
+  </si>
+  <si>
+    <t>Zhejiang Professional</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Wuhan Three Towns</t>
+  </si>
+  <si>
+    <t>Qingdao Hainiu</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
+    <t>Qingdao West Coast</t>
+  </si>
+  <si>
+    <t>Shenzhen Xinpengcheng</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Dalian Yingbo</t>
+  </si>
+  <si>
+    <t>Aarhus</t>
+  </si>
+  <si>
+    <t>Sonderjyske</t>
+  </si>
+  <si>
+    <t>Esbjerg</t>
+  </si>
+  <si>
+    <t>Brondby</t>
+  </si>
+  <si>
+    <t>FC Copenhagen</t>
+  </si>
+  <si>
+    <t>Horsens</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Odense</t>
+  </si>
+  <si>
+    <t>Aalborg</t>
+  </si>
+  <si>
+    <t>Randers FC</t>
+  </si>
+  <si>
+    <t>Nordsjaelland</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Vestsjaelland</t>
+  </si>
+  <si>
+    <t>Hobro</t>
+  </si>
+  <si>
+    <t>Lyngby</t>
+  </si>
+  <si>
+    <t>Helsingor</t>
+  </si>
+  <si>
+    <t>Vendsyssel</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Hvidovre IF</t>
+  </si>
+  <si>
+    <t>Fredericia</t>
+  </si>
+  <si>
+    <t>HJK</t>
+  </si>
+  <si>
+    <t>Honka</t>
+  </si>
+  <si>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>Lahti</t>
+  </si>
+  <si>
+    <t>TPS</t>
+  </si>
+  <si>
+    <t>JJK Jyvaskyla</t>
+  </si>
+  <si>
+    <t>Mariehamn</t>
+  </si>
+  <si>
+    <t>MyPa</t>
+  </si>
+  <si>
+    <t>VPS</t>
+  </si>
+  <si>
+    <t>Haka</t>
+  </si>
+  <si>
+    <t>Inter Turku</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
+    <t>Rovaniemi</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>KTP</t>
+  </si>
+  <si>
+    <t>HIFK</t>
+  </si>
+  <si>
+    <t>Ilves</t>
+  </si>
+  <si>
+    <t>PK-35 Vantaa</t>
+  </si>
+  <si>
+    <t>PS Kemi</t>
+  </si>
+  <si>
+    <t>KPV Kokkola</t>
+  </si>
+  <si>
+    <t>AC Oulu</t>
+  </si>
+  <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>Ekenas</t>
+  </si>
+  <si>
+    <t>Drogheda</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>St. Patricks</t>
+  </si>
+  <si>
+    <t>UC Dublin</t>
+  </si>
+  <si>
+    <t>Monaghan</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Bray</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Longford</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Limerick</t>
+  </si>
+  <si>
+    <t>Mervue</t>
+  </si>
+  <si>
+    <t>Athlone</t>
+  </si>
+  <si>
+    <t>Galway</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Cabinteely</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Gamba Osaka</t>
+  </si>
+  <si>
+    <t>Sanfrecce Hiroshima</t>
+  </si>
+  <si>
+    <t>Nagoya Grampus</t>
+  </si>
+  <si>
+    <t>Sagan Tosu</t>
+  </si>
+  <si>
+    <t>Hokkaido Consadole Sapporo</t>
+  </si>
+  <si>
+    <t>Vegalta Sendai</t>
+  </si>
+  <si>
+    <t>Kawasaki Frontale</t>
+  </si>
+  <si>
+    <t>Omiya Ardija</t>
+  </si>
+  <si>
+    <t>Kashiwa Reysol</t>
+  </si>
+  <si>
+    <t>Albirex Niigata</t>
+  </si>
+  <si>
+    <t>Cerezo Osaka</t>
+  </si>
+  <si>
+    <t>Kashima Antlers</t>
+  </si>
+  <si>
+    <t>Urawa Reds</t>
+  </si>
+  <si>
+    <t>Yokohama F. Marinos</t>
+  </si>
+  <si>
+    <t>Shimizu S-Pulse</t>
+  </si>
+  <si>
+    <t>Iwata</t>
+  </si>
+  <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
+    <t>FC Tokyo</t>
+  </si>
+  <si>
+    <t>Oita Trinita</t>
+  </si>
+  <si>
+    <t>Kofu</t>
+  </si>
+  <si>
+    <t>Shonan Bellmare</t>
+  </si>
+  <si>
+    <t>Tokushima</t>
+  </si>
+  <si>
+    <t>Yamaga</t>
+  </si>
+  <si>
+    <t>Montedio Yamagata</t>
+  </si>
+  <si>
+    <t>Avispa Fukuoka</t>
+  </si>
+  <si>
+    <t>V-Varen Nagasaki</t>
+  </si>
+  <si>
+    <t>Yokohama FC</t>
+  </si>
+  <si>
+    <t>Kyoto</t>
+  </si>
+  <si>
+    <t>Kumamoto</t>
+  </si>
+  <si>
+    <t>Okayama</t>
+  </si>
+  <si>
+    <t>Machida</t>
+  </si>
+  <si>
+    <t>Verdy</t>
+  </si>
+  <si>
+    <t>Chiapas</t>
+  </si>
+  <si>
+    <t>Club Tijuana</t>
+  </si>
+  <si>
+    <t>Cruz Azul</t>
+  </si>
+  <si>
+    <t>Queretaro</t>
+  </si>
+  <si>
+    <t>Monterrey</t>
+  </si>
+  <si>
+    <t>Santos Laguna</t>
+  </si>
+  <si>
+    <t>Atlas</t>
+  </si>
+  <si>
+    <t>Toluca</t>
+  </si>
+  <si>
+    <t>Atlante</t>
+  </si>
+  <si>
+    <t>Monarcas</t>
+  </si>
+  <si>
+    <t>Club Leon</t>
+  </si>
+  <si>
+    <t>Club America</t>
+  </si>
+  <si>
+    <t>Pachuca</t>
+  </si>
+  <si>
+    <t>Tigres UANL</t>
+  </si>
+  <si>
+    <t>Atl. San Luis</t>
+  </si>
+  <si>
+    <t>Puebla</t>
+  </si>
+  <si>
+    <t>UNAM Pumas</t>
+  </si>
+  <si>
+    <t>Guadalajara Chivas</t>
+  </si>
+  <si>
+    <t>Veracruz</t>
+  </si>
+  <si>
+    <t>Leones Negros</t>
+  </si>
+  <si>
+    <t>Dorados de Sinaloa</t>
+  </si>
+  <si>
+    <t>Necaxa</t>
+  </si>
+  <si>
+    <t>Lobos BUAP</t>
+  </si>
+  <si>
+    <t>Juarez</t>
+  </si>
+  <si>
+    <t>Mazatlan FC</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Honefoss</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Stabaek</t>
+  </si>
+  <si>
+    <t>Tromso</t>
+  </si>
+  <si>
+    <t>Valerenga</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Sandnes</t>
+  </si>
+  <si>
+    <t>Brann</t>
+  </si>
+  <si>
+    <t>Stromsgodset</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Lillestrom</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Ull/Kisa</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Bodo/Glimt</t>
+  </si>
+  <si>
+    <t>Mjondalen</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Jerv</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Ham-Kam</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>KFUM Oslo</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Pogon Szczecin</t>
+  </si>
+  <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
+    <t>Jagiellonia</t>
+  </si>
+  <si>
+    <t>Widzew Lodz</t>
+  </si>
+  <si>
+    <t>Lech Poznan</t>
+  </si>
+  <si>
+    <t>Wisla</t>
+  </si>
+  <si>
+    <t>Legia</t>
+  </si>
+  <si>
+    <t>Lechia Gdansk</t>
+  </si>
+  <si>
+    <t>Zaglebie</t>
+  </si>
+  <si>
+    <t>Podbeskidzie</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Slask Wroclaw</t>
+  </si>
+  <si>
+    <t>GKS Belchatow</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Ruch</t>
+  </si>
+  <si>
+    <t>Gornik Z.</t>
+  </si>
+  <si>
+    <t>Zawisza</t>
+  </si>
+  <si>
+    <t>Cracovia</t>
+  </si>
+  <si>
+    <t>Leczna</t>
+  </si>
+  <si>
+    <t>Termalica B-B.</t>
+  </si>
+  <si>
+    <t>Wisla Plock</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Sandecja Nowy S.</t>
+  </si>
+  <si>
+    <t>Legnica</t>
+  </si>
+  <si>
+    <t>Zaglebie Sosnowiec</t>
+  </si>
+  <si>
+    <t>LKS Lodz</t>
+  </si>
+  <si>
+    <t>Rakow</t>
+  </si>
+  <si>
+    <t>Warta Poznan</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Gornik Zabrze</t>
+  </si>
+  <si>
+    <t>Ruch Chorzow</t>
+  </si>
+  <si>
+    <t>Puszcza</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Motor Lublin</t>
+  </si>
+  <si>
+    <t>Pandurii</t>
+  </si>
+  <si>
+    <t>CS Turnu Severin</t>
+  </si>
+  <si>
+    <t>Petrolul</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Bistrita</t>
+  </si>
+  <si>
+    <t>Poli Iasi</t>
+  </si>
+  <si>
+    <t>FC Rapid Bucuresti</t>
+  </si>
+  <si>
+    <t>Viitorul Constanta</t>
+  </si>
+  <si>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>FC Brasov</t>
+  </si>
+  <si>
+    <t>Ceahlaul</t>
+  </si>
+  <si>
+    <t>Gaz Metan Medias</t>
+  </si>
+  <si>
+    <t>Astra</t>
+  </si>
+  <si>
+    <t>Vaslui</t>
+  </si>
+  <si>
+    <t>U. Cluj</t>
+  </si>
+  <si>
+    <t>Din. Bucuresti</t>
+  </si>
+  <si>
+    <t>Concordia</t>
+  </si>
+  <si>
+    <t>Otelul</t>
+  </si>
+  <si>
+    <t>Poli Timisoara</t>
+  </si>
+  <si>
+    <t>Navodari</t>
+  </si>
+  <si>
+    <t>FC Botosani</t>
+  </si>
+  <si>
+    <t>Corona Brasov</t>
+  </si>
+  <si>
+    <t>U Craiova</t>
+  </si>
+  <si>
+    <t>Targu Mures</t>
+  </si>
+  <si>
+    <t>FC Voluntari</t>
+  </si>
+  <si>
+    <t>Calarasi</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Daco-Getica Bucuresti</t>
+  </si>
+  <si>
+    <t>Sepsi Sf. Gheorghe</t>
+  </si>
+  <si>
+    <t>Chindia Targoviste</t>
+  </si>
+  <si>
+    <t>FC Hermannstadt</t>
+  </si>
+  <si>
+    <t>Academica Clinceni</t>
+  </si>
+  <si>
+    <t>Mioveni</t>
+  </si>
+  <si>
+    <t>FC Arges</t>
+  </si>
+  <si>
+    <t>Univ. Craiova</t>
+  </si>
+  <si>
+    <t>Farul Constanta</t>
+  </si>
+  <si>
+    <t>U Craiova 1948</t>
+  </si>
+  <si>
+    <t>Gloria Buzau</t>
+  </si>
+  <si>
+    <t>Csikszereda M. Ciuc</t>
+  </si>
+  <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
+    <t>Metaloglobus Bucharest</t>
+  </si>
+  <si>
+    <t>M. Saransk</t>
+  </si>
+  <si>
+    <t>CSKA Moscow</t>
+  </si>
+  <si>
+    <t>Volga N. Novgorod</t>
+  </si>
+  <si>
+    <t>Vladikavkaz</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Krylya Sovetov</t>
+  </si>
+  <si>
+    <t>FK Anzi Makhackala</t>
+  </si>
+  <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
+    <t>Kuban</t>
+  </si>
+  <si>
+    <t>Amkar</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moscow</t>
+  </si>
+  <si>
+    <t>Rubin Kazan</t>
+  </si>
+  <si>
+    <t>Spartak Moscow</t>
+  </si>
+  <si>
+    <t>FK Rostov</t>
+  </si>
+  <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
+    <t>Dynamo Moscow</t>
+  </si>
+  <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>Spartak Nalchik</t>
+  </si>
+  <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Tomsk</t>
+  </si>
+  <si>
+    <t>Ufa</t>
+  </si>
+  <si>
+    <t>T. Moscow</t>
+  </si>
+  <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
+    <t>Tosno</t>
+  </si>
+  <si>
+    <t>Volgar-Astrakhan</t>
+  </si>
+  <si>
+    <t>Orenburg</t>
+  </si>
+  <si>
+    <t>Yenisey</t>
+  </si>
+  <si>
+    <t>Tambov</t>
+  </si>
+  <si>
+    <t>Pari NN</t>
+  </si>
+  <si>
+    <t>Sochi</t>
+  </si>
+  <si>
+    <t>Khimki</t>
+  </si>
+  <si>
+    <t>R. Volgograd</t>
+  </si>
+  <si>
+    <t>Torpedo Moscow</t>
+  </si>
+  <si>
+    <t>Fakel Voronezh</t>
+  </si>
+  <si>
+    <t>Rodina Moscow</t>
+  </si>
+  <si>
+    <t>Baltika</t>
+  </si>
+  <si>
+    <t>Akron Togliatti</t>
+  </si>
+  <si>
+    <t>Dynamo Makhachkala</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Sundsvall</t>
+  </si>
+  <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Syrianska</t>
+  </si>
+  <si>
+    <t>Malmo FF</t>
+  </si>
+  <si>
+    <t>Orebro</t>
+  </si>
+  <si>
+    <t>Norrkoping</t>
+  </si>
+  <si>
+    <t>Atvidabergs</t>
+  </si>
+  <si>
+    <t>Gefle</t>
+  </si>
+  <si>
+    <t>Hacken</t>
+  </si>
+  <si>
+    <t>Mjallby</t>
+  </si>
+  <si>
+    <t>Djurgarden</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Goteborg</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Osters</t>
+  </si>
+  <si>
+    <t>Falkenbergs</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Sirius</t>
+  </si>
+  <si>
+    <t>Jonkopings</t>
+  </si>
+  <si>
+    <t>Ostersunds</t>
+  </si>
+  <si>
+    <t>AFC Eskilstuna</t>
+  </si>
+  <si>
+    <t>Trelleborgs</t>
+  </si>
+  <si>
+    <t>Dalkurd</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Varnamo</t>
+  </si>
+  <si>
+    <t>Oster</t>
+  </si>
+  <si>
+    <t>Vasteras SK</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Thun</t>
+  </si>
+  <si>
+    <t>Grasshoppers</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Lausanne</t>
+  </si>
+  <si>
+    <t>Sion</t>
+  </si>
+  <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>Zurich</t>
+  </si>
+  <si>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Lugano</t>
+  </si>
+  <si>
+    <t>Xamax</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Lausanne Ouchy</t>
+  </si>
+  <si>
+    <t>Yverdon</t>
+  </si>
+  <si>
+    <t>Colorado Rapids</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Los Angeles Galaxy</t>
+  </si>
+  <si>
+    <t>San Jose Earthquakes</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Chivas USA</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>CF Montreal</t>
+  </si>
+  <si>
+    <t>Sporting Kansas City</t>
+  </si>
+  <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Toronto FC</t>
+  </si>
+  <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>New York Red Bulls</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Atlanta Utd</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Austin FC</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>St. Louis City</t>
+  </si>
+  <si>
+    <t>San Diego FC</t>
+  </si>
+  <si>
+    <t>Schaffhausen</t>
+  </si>
+  <si>
+    <t>FA Cup</t>
   </si>
 </sst>
 </file>
@@ -453,43 +3289,71 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>955</v>
       </c>
       <c r="B2" s="2">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="C2" s="3">
-        <v>0.97916666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>955</v>
       </c>
       <c r="B3" s="2">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="C3" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="2"/>
+      <c r="A4" t="s">
+        <v>955</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46031</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.8125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="2"/>
+      <c r="A5" t="s">
+        <v>955</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46031</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.8125</v>
+      </c>
+      <c r="D5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
@@ -601,5 +3465,4777 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CCEB2945-66A9-4B6B-8C20-3A81543BAA1F}">
+          <x14:formula1>
+            <xm:f>Planilha1!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>D1:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A46D951-F2D9-406A-B03F-617E1218B6AB}">
+  <dimension ref="A1:A950"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A588" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A590" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A600" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A601" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A602" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A603" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A604" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A605" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A606" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A607" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A608" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A609" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A610" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A611" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A612" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A613" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A614" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A615" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A616" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A617" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A618" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A619" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A620" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A621" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A622" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A623" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A624" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A625" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A626" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A627" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A628" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A629" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A630" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A631" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A632" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A633" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A634" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A635" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A636" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A637" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A638" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A639" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A640" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A641" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A642" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A643" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A644" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A645" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A646" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A647" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A648" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A649" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A658" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A659" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A660" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A663" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A664" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A665" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A666" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A667" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A668" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A669" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A670" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A671" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A672" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A673" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="683" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A684" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A688" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="689" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A691" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A692" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A694" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="695" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A696" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A697" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A698" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A700" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="701" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A702" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A703" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A704" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A706" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="707" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A708" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A709" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A710" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A712" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="713" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A714" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A715" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A716" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A717" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A718" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="719" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A719" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A720" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A721" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A722" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A723" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A724" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A725" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A726" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A727" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A728" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A729" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="730" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A730" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="731" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A732" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A733" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A734" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="736" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A736" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="737" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="738" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A738" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="739" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A739" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="740" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A740" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="741" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A741" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="742" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A742" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="743" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A743" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="744" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A744" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="745" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A745" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="746" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A746" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="747" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A747" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="748" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A748" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="749" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="750" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A750" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="751" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A751" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="752" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A752" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="753" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="754" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A754" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="755" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="756" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A756" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="757" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A757" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="758" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A758" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="759" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A759" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="760" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A760" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="761" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A761" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="762" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A762" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="763" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A763" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="764" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A764" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="765" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A765" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="766" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A766" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="767" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A767" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="768" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A768" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="769" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A769" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="770" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A770" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="771" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A771" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="772" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A772" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="773" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A773" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="774" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A774" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="775" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A775" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="776" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A776" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="777" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A777" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="778" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A778" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="779" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A779" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="780" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A780" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="781" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A781" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="782" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A782" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="783" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A783" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="784" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A784" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="785" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A785" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="786" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A786" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="787" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A787" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="788" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A788" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="789" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A789" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="790" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A790" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="791" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A791" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="792" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A792" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="793" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A793" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="794" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A794" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="795" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A795" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="796" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A796" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="797" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A797" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="798" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A798" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="799" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A799" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="800" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A800" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="801" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A801" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="802" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A802" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="803" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A803" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="804" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A804" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="805" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A805" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="806" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A806" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="807" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A807" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="808" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A808" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="809" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A809" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="810" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A810" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="811" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A811" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="812" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A812" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="813" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A813" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="814" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A814" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="815" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A815" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="816" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A816" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="817" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A817" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="818" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A818" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="819" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A819" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="820" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A820" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="821" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A821" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="822" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A822" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="823" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A823" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="824" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A824" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="825" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A825" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="826" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A826" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="827" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A827" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="828" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A828" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="829" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A829" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="830" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A830" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="831" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A831" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="832" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A832" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="833" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A833" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="834" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A834" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="835" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A835" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="836" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A836" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="837" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A837" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="838" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A838" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="839" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A839" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="840" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A840" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="841" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A841" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="842" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A842" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="843" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A843" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="844" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A844" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="845" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A845" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="846" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A846" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="847" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A847" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="848" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A848" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="849" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A849" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="850" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A850" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="851" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A851" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="852" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A852" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="853" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A853" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="854" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A854" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="855" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A855" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="856" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A856" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="857" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A857" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="858" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A858" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="859" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A859" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="860" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A860" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="861" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A861" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="862" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A862" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="863" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A863" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="864" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A864" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="865" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A865" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="866" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A866" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="867" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A867" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="868" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A868" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="869" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A869" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="870" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A870" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="871" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A871" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="872" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A872" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="873" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A873" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="874" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A874" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="875" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A875" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="876" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A876" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="877" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A877" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="878" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A878" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="879" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A879" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="880" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A880" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="881" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A881" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="882" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A882" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="883" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A883" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="884" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A884" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="885" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A885" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="886" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A886" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="887" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A887" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="888" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A888" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="889" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A889" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="890" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A890" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="891" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A891" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="892" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A892" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="893" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A893" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="894" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A894" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="895" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A895" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="896" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A896" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="897" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A897" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="898" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A898" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="899" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A899" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="900" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A900" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="901" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A901" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="902" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A902" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="903" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A903" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="904" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A904" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="905" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A905" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="906" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A906" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="907" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A907" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="908" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A908" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="909" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A909" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="910" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A910" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="911" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A911" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="912" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A912" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="913" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A913" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="914" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A914" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="915" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A915" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="916" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A916" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="917" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A917" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="918" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A918" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="919" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A919" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="920" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A920" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="921" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A921" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="922" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A922" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="923" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A923" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="924" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A924" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="925" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A925" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="926" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A926" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="927" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A927" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="928" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A928" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="929" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A929" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="930" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A930" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="931" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A931" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="932" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A932" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="933" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A933" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="934" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A934" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="935" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A935" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="936" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A936" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="937" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A937" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="938" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A938" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="939" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A939" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="940" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A940" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="941" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A941" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="942" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A942" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="943" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A943" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="944" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A944" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="945" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A945" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="946" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A946" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="947" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A947" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="948" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A948" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="949" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A949" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="950" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A950" t="s">
+        <v>954</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60EADD5-2A48-4AA5-90FA-8EB05B7E7186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E469F5C9-B28B-4FC0-AD86-E6D283C8B1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12504" yWindow="1116" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="956">
   <si>
     <t>Div</t>
   </si>
@@ -2888,7 +2888,7 @@
     <t>Schaffhausen</t>
   </si>
   <si>
-    <t>FA Cup</t>
+    <t>Liga MX</t>
   </si>
 </sst>
 </file>
@@ -2898,7 +2898,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2914,16 +2914,308 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2946,20 +3238,210 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bom" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Célula Vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Ênfase1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Ênfase2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Ênfase3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Ênfase4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3261,7 +3743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
@@ -3288,72 +3770,44 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>955</v>
       </c>
       <c r="B2" s="2">
         <v>46031</v>
       </c>
       <c r="C2" s="3">
-        <v>0.8125</v>
+        <v>0.99930555555555556</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>707</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>716</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>955</v>
       </c>
       <c r="B3" s="2">
         <v>46031</v>
       </c>
       <c r="C3" s="3">
-        <v>0.8125</v>
+        <v>0.99930555555555556</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>702</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>955</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46031</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.8125</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>76</v>
-      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>955</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46031</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.8125</v>
-      </c>
-      <c r="D5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
@@ -3456,12 +3910,6 @@
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B40" s="2"/>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B41" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E469F5C9-B28B-4FC0-AD86-E6D283C8B1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030779E7-A9D5-490F-94E2-804493480D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10728" yWindow="1008" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="959">
   <si>
     <t>Div</t>
   </si>
@@ -2888,7 +2888,16 @@
     <t>Schaffhausen</t>
   </si>
   <si>
-    <t>Liga MX</t>
+    <t>Copa EFL</t>
+  </si>
+  <si>
+    <t>Copa do Rei</t>
+  </si>
+  <si>
+    <t>Copa da Itali</t>
+  </si>
+  <si>
+    <t>Copa da Holanda</t>
   </si>
 </sst>
 </file>
@@ -3390,14 +3399,13 @@
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3743,7 +3751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
@@ -3770,50 +3778,106 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
         <v>955</v>
       </c>
       <c r="B2" s="2">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="C2" s="3">
-        <v>0.99930555555555556</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D2" t="s">
-        <v>707</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>716</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>955</v>
+      <c r="A3" t="s">
+        <v>956</v>
       </c>
       <c r="B3" s="2">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="C3" s="3">
-        <v>0.99930555555555556</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D3" t="s">
-        <v>702</v>
+        <v>443</v>
       </c>
       <c r="E3" t="s">
-        <v>712</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="2"/>
+      <c r="A4" t="s">
+        <v>956</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46035</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D4" t="s">
+        <v>412</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="2"/>
+      <c r="A5" t="s">
+        <v>956</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46035</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E5" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="2"/>
+      <c r="A6" t="s">
+        <v>957</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46035</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
+      <c r="A7" t="s">
+        <v>958</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46035</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E7" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
@@ -3877,39 +3941,6 @@
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="2"/>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B30" s="2"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B36" s="2"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B38" s="2"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B39" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030779E7-A9D5-490F-94E2-804493480D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D75FDC6-C8A9-47F1-8A59-9EFB10CCB998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10728" yWindow="1008" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="960">
   <si>
     <t>Div</t>
   </si>
@@ -2894,10 +2894,13 @@
     <t>Copa do Rei</t>
   </si>
   <si>
-    <t>Copa da Itali</t>
-  </si>
-  <si>
     <t>Copa da Holanda</t>
+  </si>
+  <si>
+    <t>Copa da Belgica</t>
+  </si>
+  <si>
+    <t>Copa da Grecia</t>
   </si>
 </sst>
 </file>
@@ -3751,7 +3754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
@@ -3782,33 +3785,33 @@
         <v>955</v>
       </c>
       <c r="B2" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="C2" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B3" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="C3" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D3" t="s">
-        <v>443</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3816,7 +3819,7 @@
         <v>956</v>
       </c>
       <c r="B4" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="C4" s="3">
         <v>0.83333333333333337</v>
@@ -3833,60 +3836,102 @@
         <v>956</v>
       </c>
       <c r="B5" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="C5" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B6" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="C6" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B7" s="2">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="C7" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D7" t="s">
-        <v>349</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>351</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
+      <c r="A8" t="s">
+        <v>958</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46036</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.8125</v>
+      </c>
+      <c r="D8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E8" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
+      <c r="A9" t="s">
+        <v>959</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46036</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E9" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
+      <c r="A10" t="s">
+        <v>957</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46036</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E10" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
@@ -3932,15 +3977,6 @@
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D75FDC6-C8A9-47F1-8A59-9EFB10CCB998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791CE5BF-B1A3-49D4-8A9C-AA2C02B19FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10728" yWindow="1008" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="956">
   <si>
     <t>Div</t>
   </si>
@@ -2888,19 +2888,7 @@
     <t>Schaffhausen</t>
   </si>
   <si>
-    <t>Copa EFL</t>
-  </si>
-  <si>
     <t>Copa do Rei</t>
-  </si>
-  <si>
-    <t>Copa da Holanda</t>
-  </si>
-  <si>
-    <t>Copa da Belgica</t>
-  </si>
-  <si>
-    <t>Copa da Grecia</t>
   </si>
 </sst>
 </file>
@@ -3754,7 +3742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
@@ -3785,16 +3773,16 @@
         <v>955</v>
       </c>
       <c r="B2" s="2">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="C2" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>226</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3802,136 +3790,38 @@
         <v>955</v>
       </c>
       <c r="B3" s="2">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="C3" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>223</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>956</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46036</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>956</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46036</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E5" t="s">
-        <v>220</v>
-      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>956</v>
-      </c>
-      <c r="B6" s="2">
-        <v>46036</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D6" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" t="s">
-        <v>225</v>
-      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>956</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46036</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>958</v>
-      </c>
-      <c r="B8" s="2">
-        <v>46036</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.8125</v>
-      </c>
-      <c r="D8" t="s">
-        <v>423</v>
-      </c>
-      <c r="E8" t="s">
-        <v>319</v>
-      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>959</v>
-      </c>
-      <c r="B9" s="2">
-        <v>46036</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D9" t="s">
-        <v>343</v>
-      </c>
-      <c r="E9" t="s">
-        <v>453</v>
-      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>957</v>
-      </c>
-      <c r="B10" s="2">
-        <v>46036</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D10" t="s">
-        <v>348</v>
-      </c>
-      <c r="E10" t="s">
-        <v>344</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
@@ -3953,30 +3843,6 @@
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791CE5BF-B1A3-49D4-8A9C-AA2C02B19FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AA7EE2-1322-430D-9415-95E0B5E036C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10728" yWindow="1008" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="957">
   <si>
     <t>Div</t>
   </si>
@@ -2889,6 +2889,9 @@
   </si>
   <si>
     <t>Copa do Rei</t>
+  </si>
+  <si>
+    <t>Paulista</t>
   </si>
 </sst>
 </file>
@@ -3803,7 +3806,21 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="2"/>
+      <c r="A4" t="s">
+        <v>956</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46037</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D4" t="s">
+        <v>555</v>
+      </c>
+      <c r="E4" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AA7EE2-1322-430D-9415-95E0B5E036C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B9045F-C22E-4B2E-9F28-980CD2C08130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10728" yWindow="1008" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="1704" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="956">
   <si>
     <t>Div</t>
   </si>
@@ -2888,10 +2888,7 @@
     <t>Schaffhausen</t>
   </si>
   <si>
-    <t>Copa do Rei</t>
-  </si>
-  <si>
-    <t>Paulista</t>
+    <t>Champions League</t>
   </si>
 </sst>
 </file>
@@ -3745,7 +3742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
@@ -3776,16 +3773,16 @@
         <v>955</v>
       </c>
       <c r="B2" s="2">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="C2" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.73958333333333337</v>
       </c>
       <c r="D2" t="s">
-        <v>226</v>
+        <v>746</v>
       </c>
       <c r="E2" t="s">
-        <v>213</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3793,49 +3790,119 @@
         <v>955</v>
       </c>
       <c r="B3" s="2">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="C3" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D3" t="s">
-        <v>223</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>216</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B4" s="2">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="C4" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D4" t="s">
-        <v>555</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>526</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="2"/>
+      <c r="A5" t="s">
+        <v>955</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46042</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="2"/>
+      <c r="A6" t="s">
+        <v>955</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46042</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
+      <c r="A7" t="s">
+        <v>955</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46042</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
+      <c r="A8" t="s">
+        <v>955</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46042</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+      <c r="E8" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
+      <c r="A9" t="s">
+        <v>955</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46042</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D9" t="s">
+        <v>606</v>
+      </c>
+      <c r="E9" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
@@ -3851,15 +3918,6 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B9045F-C22E-4B2E-9F28-980CD2C08130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD8F918-893B-4D6E-97C6-8C9A05B2FF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="1704" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD8F918-893B-4D6E-97C6-8C9A05B2FF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FB3D28-8CDD-4DAD-8AB4-5A19E4C5783E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12468" yWindow="2748" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="956">
   <si>
     <t>Div</t>
   </si>
@@ -3742,7 +3742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
@@ -3773,16 +3773,16 @@
         <v>955</v>
       </c>
       <c r="B2" s="2">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="C2" s="3">
         <v>0.73958333333333337</v>
       </c>
       <c r="D2" t="s">
-        <v>746</v>
+        <v>384</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3790,16 +3790,16 @@
         <v>955</v>
       </c>
       <c r="B3" s="2">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="C3" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.73958333333333337</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="E3" t="s">
-        <v>297</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3807,16 +3807,16 @@
         <v>955</v>
       </c>
       <c r="B4" s="2">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="C4" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3824,16 +3824,16 @@
         <v>955</v>
       </c>
       <c r="B5" s="2">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="C5" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D5" t="s">
-        <v>209</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>338</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3841,68 +3841,28 @@
         <v>955</v>
       </c>
       <c r="B6" s="2">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="C6" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>173</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>955</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46042</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D7" t="s">
-        <v>356</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>955</v>
-      </c>
-      <c r="B8" s="2">
-        <v>46042</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D8" t="s">
-        <v>395</v>
-      </c>
-      <c r="E8" t="s">
-        <v>170</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>955</v>
-      </c>
-      <c r="B9" s="2">
-        <v>46042</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D9" t="s">
-        <v>606</v>
-      </c>
-      <c r="E9" t="s">
-        <v>259</v>
-      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
@@ -3912,12 +3872,6 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FB3D28-8CDD-4DAD-8AB4-5A19E4C5783E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B91EB0-44B4-4862-864E-FF374A906DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12468" yWindow="2748" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8760" yWindow="2076" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="956">
   <si>
     <t>Div</t>
   </si>
@@ -3742,9 +3742,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -3773,16 +3774,16 @@
         <v>955</v>
       </c>
       <c r="B2" s="2">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="C2" s="3">
-        <v>0.73958333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>384</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3790,16 +3791,16 @@
         <v>955</v>
       </c>
       <c r="B3" s="2">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="C3" s="3">
-        <v>0.73958333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D3" t="s">
-        <v>262</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3807,16 +3808,16 @@
         <v>955</v>
       </c>
       <c r="B4" s="2">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="C4" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
-        <v>365</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3824,16 +3825,16 @@
         <v>955</v>
       </c>
       <c r="B5" s="2">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="C5" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>216</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3841,37 +3842,187 @@
         <v>955</v>
       </c>
       <c r="B6" s="2">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="C6" s="3">
         <v>0.83333333333333337</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>955</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>955</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D8" t="s">
+        <v>365</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>955</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>955</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D10" t="s">
+        <v>325</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>955</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D11" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="2"/>
+      <c r="E11" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
+      <c r="A12" t="s">
+        <v>955</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E12" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>955</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>955</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>955</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D15" t="s">
+        <v>319</v>
+      </c>
+      <c r="E15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>955</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" t="s">
+        <v>356</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/base/JogosAdicionais.xlsx
+++ b/base/JogosAdicionais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B91EB0-44B4-4862-864E-FF374A906DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEA36BB-2437-4A99-BEFD-FAD6F546A0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="2076" windowWidth="10464" windowHeight="10164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="957">
   <si>
     <t>Div</t>
   </si>
@@ -2889,6 +2889,9 @@
   </si>
   <si>
     <t>Champions League</t>
+  </si>
+  <si>
+    <t>Brasileirão</t>
   </si>
 </sst>
 </file>
@@ -3742,7 +3745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -4022,6 +4025,23 @@
       </c>
       <c r="E16" t="s">
         <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>956</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46050</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D17" t="s">
+        <v>526</v>
+      </c>
+      <c r="E17" t="s">
+        <v>529</v>
       </c>
     </row>
   </sheetData>
